--- a/dcf/NTRA.xlsx
+++ b/dcf/NTRA.xlsx
@@ -1138,184 +1138,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>26.88096349236418</v>
+        <v>35.74262259788173</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>25.82011801110819</v>
+        <v>34.28843944699563</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>24.81106133629187</v>
+        <v>32.90516470925285</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>23.85109548468245</v>
+        <v>31.58909100973687</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>22.93767406709733</v>
+        <v>30.33672004402366</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>22.06839313541854</v>
+        <v>29.14474991605851</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>21.24098262038953</v>
+        <v>28.0100632953634</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>29.09637826874357</v>
+        <v>37.95803737426111</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>27.93719837008005</v>
+        <v>36.40551980596749</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>26.83458717953211</v>
+        <v>34.92869055249309</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>25.78559436594606</v>
+        <v>33.52358989100048</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>24.78743556132891</v>
+        <v>32.18648153825524</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>23.83748233057853</v>
+        <v>30.9138391112185</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>22.933252789133</v>
+        <v>29.70233346410686</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>31.31179304512296</v>
+        <v>40.1734521506405</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>30.05427872905191</v>
+        <v>38.52260016493934</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>28.85811302277236</v>
+        <v>36.95221639573334</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>27.72009324720966</v>
+        <v>35.45808877226408</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>26.63719705556049</v>
+        <v>34.03624303248682</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>25.60657152573852</v>
+        <v>32.68292830637849</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>24.62552295787646</v>
+        <v>31.39460363285033</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>33.52720782150234</v>
+        <v>42.38886692701988</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>32.17135908802377</v>
+        <v>40.6396805239112</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>30.88163886601261</v>
+        <v>38.97574223897358</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>29.65459212847327</v>
+        <v>37.39258765352768</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>28.48695854979208</v>
+        <v>35.8860045267184</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>27.37566072089852</v>
+        <v>34.45201750153849</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>26.31779312661993</v>
+        <v>33.08687380159379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>35.74262259788173</v>
+        <v>44.60428170339927</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>34.28843944699563</v>
+        <v>42.75676088288306</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>32.90516470925285</v>
+        <v>40.99926808221383</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>31.58909100973687</v>
+        <v>39.32708653479129</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>30.33672004402366</v>
+        <v>37.73576602094998</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>29.14474991605851</v>
+        <v>36.22110669669848</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>28.0100632953634</v>
+        <v>34.77914397033725</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>37.95803737426111</v>
+        <v>46.81969647977865</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>36.40551980596749</v>
+        <v>44.87384124185492</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>34.92869055249309</v>
+        <v>43.02279392545407</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>33.52358989100048</v>
+        <v>41.26158541605489</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>32.18648153825524</v>
+        <v>39.58552751518157</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>30.9138391112185</v>
+        <v>37.99019589185847</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>29.70233346410686</v>
+        <v>36.47141413908071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>40.1734521506405</v>
+        <v>49.03511125615803</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>38.52260016493934</v>
+        <v>46.99092160082678</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>36.95221639573334</v>
+        <v>45.04631976869432</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>35.45808877226408</v>
+        <v>43.1960842973185</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>34.03624303248682</v>
+        <v>41.43528900941315</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>32.68292830637849</v>
+        <v>39.75928508701845</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>31.39460363285033</v>
+        <v>38.16368430782418</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
         <v>0.113782395450345</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.6473496805016535</v>
+        <v>0.6452615956712952</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24401,7 +24401,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>29.65459212847327</v>
+        <v>37.39258765352768</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>47.5960999125399</v>
+        <v>58.36430946775298</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>17.14604014189313</v>
+        <v>22.53292185075521</v>
       </c>
     </row>
     <row r="59">

--- a/dcf/NTRA.xlsx
+++ b/dcf/NTRA.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1141,25 +1141,25 @@
         <v>13</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>35.74262259788173</v>
+        <v>30.34744193054087</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>34.28843944699563</v>
+        <v>29.12804872956494</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>32.90516470925285</v>
+        <v>27.96834468686115</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>31.58909100973687</v>
+        <v>26.8652071677405</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>30.33672004402366</v>
+        <v>25.81568963216144</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>29.14474991605851</v>
+        <v>24.81701097099919</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>28.0100632953634</v>
+        <v>23.86654553225004</v>
       </c>
     </row>
     <row r="6">
@@ -1167,25 +1167,25 @@
         <v>14</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>37.95803737426111</v>
+        <v>32.21174539907501</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>36.40551980596749</v>
+        <v>30.9096023684041</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>34.92869055249309</v>
+        <v>29.67117085216575</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>33.52358989100048</v>
+        <v>28.49311586125801</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>32.18648153825524</v>
+        <v>27.37229059304006</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>30.9138391112185</v>
+        <v>26.30572502935404</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>29.70233346410686</v>
+        <v>25.29061527256355</v>
       </c>
     </row>
     <row r="7">
@@ -1193,25 +1193,25 @@
         <v>15</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>40.1734521506405</v>
+        <v>34.07604886760915</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>38.52260016493934</v>
+        <v>32.69115600724326</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>36.95221639573334</v>
+        <v>31.37399701747035</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>35.45808877226408</v>
+        <v>30.12102455477553</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>34.03624303248682</v>
+        <v>28.92889155391868</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>32.68292830637849</v>
+        <v>27.79443908770888</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>31.39460363285033</v>
+        <v>26.71468501287705</v>
       </c>
     </row>
     <row r="8">
@@ -1219,25 +1219,25 @@
         <v>16</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>42.38886692701988</v>
+        <v>35.94035233614328</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>40.6396805239112</v>
+        <v>34.47270964608243</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>38.97574223897358</v>
+        <v>33.07682318277495</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>37.39258765352768</v>
+        <v>31.74893324829304</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>35.8860045267184</v>
+        <v>30.48549251479729</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>34.45201750153849</v>
+        <v>29.28315314606373</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>33.08687380159379</v>
+        <v>28.13875475319056</v>
       </c>
     </row>
     <row r="9">
@@ -1245,25 +1245,25 @@
         <v>17</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>44.60428170339927</v>
+        <v>37.80465580467743</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>42.75676088288306</v>
+        <v>36.25426328492159</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>40.99926808221383</v>
+        <v>34.77964934807956</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>39.32708653479129</v>
+        <v>33.37684194181055</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>37.73576602094998</v>
+        <v>32.04209347567591</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>36.22110669669848</v>
+        <v>30.77186720441857</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>34.77914397033725</v>
+        <v>29.56282449350407</v>
       </c>
     </row>
     <row r="10">
@@ -1271,25 +1271,25 @@
         <v>18</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>46.81969647977865</v>
+        <v>39.66895927321158</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>44.87384124185492</v>
+        <v>38.03581692376074</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>43.02279392545407</v>
+        <v>36.48247551338416</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>41.26158541605489</v>
+        <v>35.00475063532807</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>39.58552751518157</v>
+        <v>33.59869443655452</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>37.99019589185847</v>
+        <v>32.26058126277341</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>36.47141413908071</v>
+        <v>30.98689423381757</v>
       </c>
     </row>
     <row r="11">
@@ -1297,25 +1297,25 @@
         <v>19</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>49.03511125615803</v>
+        <v>41.53326274174571</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>46.99092160082678</v>
+        <v>39.8173705625999</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>45.04631976869432</v>
+        <v>38.18530167868876</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>43.1960842973185</v>
+        <v>36.63265932884558</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>41.43528900941315</v>
+        <v>35.15529539743314</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>39.75928508701845</v>
+        <v>33.74929532112826</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>38.16368430782418</v>
+        <v>32.41096397413109</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.6452615956712952</v>
+        <v>0.6405336726094594</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>37.39258765352768</v>
+        <v>31.74893324829304</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>58.36430946775298</v>
+        <v>48.43917269113394</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>22.53292185075521</v>
+        <v>19.57600554868631</v>
       </c>
     </row>
     <row r="59">
